--- a/data/trans_orig/P37-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2007</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>52450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57290</t>
+          <t>55801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89685</t>
+          <t>87018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219606</t>
+          <t>219646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242772</t>
+          <t>242891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217731</t>
+          <t>218152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238917</t>
+          <t>239585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443249</t>
+          <t>445916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475644</t>
+          <t>477133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>38743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50037</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79313</t>
+          <t>76636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93652</t>
+          <t>94227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133610</t>
+          <t>134998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427255</t>
+          <t>426728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455805</t>
+          <t>454332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423655</t>
+          <t>426332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452931</t>
+          <t>454239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862433</t>
+          <t>861045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902391</t>
+          <t>901816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61069</t>
+          <t>62692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>49544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77253</t>
+          <t>78366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94731</t>
+          <t>93328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>130501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257777</t>
+          <t>256154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282054</t>
+          <t>282201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258159</t>
+          <t>257046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285943</t>
+          <t>285868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>520577</t>
+          <t>523757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559527</t>
+          <t>560930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57077</t>
+          <t>56365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48188</t>
+          <t>49224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74720</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86500</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123431</t>
+          <t>124267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301594</t>
+          <t>302306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326870</t>
+          <t>325502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296736</t>
+          <t>295431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323268</t>
+          <t>322232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606696</t>
+          <t>605860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>643627</t>
+          <t>641556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42804</t>
+          <t>42512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57803</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88496</t>
+          <t>89512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160504</t>
+          <t>160796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181072</t>
+          <t>181322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151071</t>
+          <t>152938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176684</t>
+          <t>175926</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321564</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352257</t>
+          <t>351946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37764</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63404</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100662</t>
+          <t>102727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223229</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244959</t>
+          <t>245471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214740</t>
+          <t>215423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240380</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>448293</t>
+          <t>446228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481899</t>
+          <t>479961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>77020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111247</t>
+          <t>112725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92305</t>
+          <t>92520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128981</t>
+          <t>130636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174095</t>
+          <t>177884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227754</t>
+          <t>229114</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502930</t>
+          <t>501452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539281</t>
+          <t>537157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>509238</t>
+          <t>507583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545914</t>
+          <t>545699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1024642</t>
+          <t>1023282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1078301</t>
+          <t>1074512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95133</t>
+          <t>94366</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134625</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97026</t>
+          <t>96679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>138743</t>
+          <t>138294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>204022</t>
+          <t>204039</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>256731</t>
+          <t>260040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>609170</t>
+          <t>609855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>648662</t>
+          <t>649429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>644768</t>
+          <t>645217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>686485</t>
+          <t>686832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1270575</t>
+          <t>1267266</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1323284</t>
+          <t>1323267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>417913</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>490166</t>
+          <t>490096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>494083</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>576847</t>
+          <t>574991</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>936157</t>
+          <t>933527</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1051755</t>
+          <t>1045896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2784613</t>
+          <t>2784683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2859559</t>
+          <t>2856866</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2800453</t>
+          <t>2802309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2885908</t>
+          <t>2883217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5600324</t>
+          <t>5606183</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5715922</t>
+          <t>5718552</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2012</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37792</t>
+          <t>37373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64894</t>
+          <t>63472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35180</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62694</t>
+          <t>62556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78913</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116162</t>
+          <t>118129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229844</t>
+          <t>231266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256946</t>
+          <t>257365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224551</t>
+          <t>224689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252065</t>
+          <t>251657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465821</t>
+          <t>463854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503070</t>
+          <t>504130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>73517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110164</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>74475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108783</t>
+          <t>109852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156001</t>
+          <t>153784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207975</t>
+          <t>205315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395363</t>
+          <t>394933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433479</t>
+          <t>432010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>414982</t>
+          <t>413913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450726</t>
+          <t>449290</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>821317</t>
+          <t>823977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873291</t>
+          <t>875508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>82582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79984</t>
+          <t>79161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110943</t>
+          <t>111325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150840</t>
+          <t>152660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238293</t>
+          <t>239490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269226</t>
+          <t>268985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259965</t>
+          <t>260788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288408</t>
+          <t>289491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>511181</t>
+          <t>509361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>551078</t>
+          <t>550696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>51488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83817</t>
+          <t>83142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110634</t>
+          <t>110358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136417</t>
+          <t>135796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182783</t>
+          <t>184772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290165</t>
+          <t>290840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322003</t>
+          <t>322494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>278317</t>
+          <t>278593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313546</t>
+          <t>312324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580150</t>
+          <t>578161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626516</t>
+          <t>627137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>48457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93935</t>
+          <t>96150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162710</t>
+          <t>163146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186580</t>
+          <t>186803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164242</t>
+          <t>164136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188548</t>
+          <t>188682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337259</t>
+          <t>335044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>368299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44587</t>
+          <t>45325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>73968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>51276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79998</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102723</t>
+          <t>103148</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144269</t>
+          <t>141204</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202440</t>
+          <t>200013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229394</t>
+          <t>228656</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200033</t>
+          <t>201337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228452</t>
+          <t>228755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>409743</t>
+          <t>412808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451289</t>
+          <t>450864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94091</t>
+          <t>92674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134809</t>
+          <t>135088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>98909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138535</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201726</t>
+          <t>204398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>260984</t>
+          <t>262817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>527979</t>
+          <t>527700</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>568697</t>
+          <t>570114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>555318</t>
+          <t>555771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598116</t>
+          <t>594944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1095657</t>
+          <t>1093824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1154915</t>
+          <t>1152243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103192</t>
+          <t>103779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146721</t>
+          <t>146643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110767</t>
+          <t>111937</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154901</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>226509</t>
+          <t>227879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>288915</t>
+          <t>290242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630342</t>
+          <t>630420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>673871</t>
+          <t>673284</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>668509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>713086</t>
+          <t>711916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1312001</t>
+          <t>1310674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1374407</t>
+          <t>1373037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>559635</t>
+          <t>561934</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>654722</t>
+          <t>651223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>602855</t>
+          <t>603682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>697599</t>
+          <t>697331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1188426</t>
+          <t>1180465</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1318334</t>
+          <t>1318056</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2767033</t>
+          <t>2770532</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2862120</t>
+          <t>2859821</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2859639</t>
+          <t>2859907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2954383</t>
+          <t>2953556</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5660659</t>
+          <t>5660937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5790567</t>
+          <t>5798528</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2016</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32880</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>56833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>62467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72529</t>
+          <t>71444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107477</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236549</t>
+          <t>236928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260881</t>
+          <t>262612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228024</t>
+          <t>226236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254777</t>
+          <t>253727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474987</t>
+          <t>472041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>509935</t>
+          <t>511020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65203</t>
+          <t>64819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>97940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53537</t>
+          <t>55402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88443</t>
+          <t>86550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129046</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175752</t>
+          <t>174424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403257</t>
+          <t>404635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437372</t>
+          <t>437756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>434641</t>
+          <t>436534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469547</t>
+          <t>467682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849907</t>
+          <t>851235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896613</t>
+          <t>901085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73638</t>
+          <t>73869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89132</t>
+          <t>89600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113348</t>
+          <t>114399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154845</t>
+          <t>155894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244927</t>
+          <t>244696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>271080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247177</t>
+          <t>246709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278578</t>
+          <t>278607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500029</t>
+          <t>498980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541526</t>
+          <t>540475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58267</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>87550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99211</t>
+          <t>99910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129081</t>
+          <t>129577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177797</t>
+          <t>178476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281893</t>
+          <t>282414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311697</t>
+          <t>312542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288072</t>
+          <t>287373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322042</t>
+          <t>319918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579450</t>
+          <t>578771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>628166</t>
+          <t>627670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73967</t>
+          <t>73611</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172922</t>
+          <t>172557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190951</t>
+          <t>191743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>175989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198162</t>
+          <t>197673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355841</t>
+          <t>356197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384161</t>
+          <t>385861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38641</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>63893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50298</t>
+          <t>50435</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97382</t>
+          <t>95226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135373</t>
+          <t>135454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199402</t>
+          <t>199230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224482</t>
+          <t>224724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193665</t>
+          <t>194646</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>222680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400865</t>
+          <t>400784</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>438856</t>
+          <t>441012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89212</t>
+          <t>90298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129540</t>
+          <t>129954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>113346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156634</t>
+          <t>157134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214960</t>
+          <t>214920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274645</t>
+          <t>274718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>527018</t>
+          <t>526604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>567346</t>
+          <t>566260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>534660</t>
+          <t>534160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>578302</t>
+          <t>577948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1073207</t>
+          <t>1073134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1132892</t>
+          <t>1132932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77406</t>
+          <t>76996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113889</t>
+          <t>112884</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94039</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134300</t>
+          <t>138346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180186</t>
+          <t>182422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237825</t>
+          <t>237269</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>664694</t>
+          <t>665699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>701177</t>
+          <t>701587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>691867</t>
+          <t>687821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>730843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1366925</t>
+          <t>1367481</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1424564</t>
+          <t>1422328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>493254</t>
+          <t>496907</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>581097</t>
+          <t>576882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>564712</t>
+          <t>568059</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>659929</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1079768</t>
+          <t>1085633</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1209766</t>
+          <t>1210414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2813253</t>
+          <t>2817468</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2901096</t>
+          <t>2897443</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2884613</t>
+          <t>2880519</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2979830</t>
+          <t>2976483</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5729126</t>
+          <t>5728478</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5859124</t>
+          <t>5853259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2023</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>71781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110054</t>
+          <t>106535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91636</t>
+          <t>92515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>118940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171168</t>
+          <t>174264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216009</t>
+          <t>216546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>201389</t>
+          <t>204908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237966</t>
+          <t>239662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170426</t>
+          <t>170695</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197999</t>
+          <t>197120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>385068</t>
+          <t>384531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>429909</t>
+          <t>426813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118819</t>
+          <t>116303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>163911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142939</t>
+          <t>142478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179134</t>
+          <t>179434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>270634</t>
+          <t>271377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>331013</t>
+          <t>333163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353595</t>
+          <t>354479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399571</t>
+          <t>402087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335835</t>
+          <t>335535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372030</t>
+          <t>372491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702346</t>
+          <t>700196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>762725</t>
+          <t>761982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72137</t>
+          <t>71874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101065</t>
+          <t>100563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95739</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122974</t>
+          <t>122824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177725</t>
+          <t>175578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215698</t>
+          <t>217095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214985</t>
+          <t>215487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243913</t>
+          <t>244176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226154</t>
+          <t>226304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253389</t>
+          <t>255005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>449480</t>
+          <t>448083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>487453</t>
+          <t>489600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82022</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119727</t>
+          <t>119202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82708</t>
+          <t>80836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172427</t>
+          <t>173707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180979</t>
+          <t>171174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280552</t>
+          <t>278664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192830</t>
+          <t>193355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230535</t>
+          <t>229722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303291</t>
+          <t>302011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>393010</t>
+          <t>394882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>507722</t>
+          <t>509610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>607295</t>
+          <t>617100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45540</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66150</t>
+          <t>66591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72131</t>
+          <t>71444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90863</t>
+          <t>90516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123208</t>
+          <t>124247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150342</t>
+          <t>150431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112592</t>
+          <t>112151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133202</t>
+          <t>132427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117411</t>
+          <t>117758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136143</t>
+          <t>136830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236674</t>
+          <t>236585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263808</t>
+          <t>262769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>59758</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82845</t>
+          <t>83287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84093</t>
+          <t>84117</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107022</t>
+          <t>106333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150565</t>
+          <t>148471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184004</t>
+          <t>183570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186791</t>
+          <t>186349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208316</t>
+          <t>209878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150034</t>
+          <t>150723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172963</t>
+          <t>172939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342688</t>
+          <t>343122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>376127</t>
+          <t>378221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172026</t>
+          <t>172680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221126</t>
+          <t>221961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>297942</t>
+          <t>297467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621831</t>
+          <t>646574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>486364</t>
+          <t>484226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>953869</t>
+          <t>925864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>403153</t>
+          <t>402318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>452253</t>
+          <t>451599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227434</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>551323</t>
+          <t>551798</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>519675</t>
+          <t>547680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>987180</t>
+          <t>989318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>365814</t>
+          <t>367764</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279028</t>
+          <t>279244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323051</t>
+          <t>326040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354399</t>
+          <t>350951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>674165</t>
+          <t>676617</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>562906</t>
+          <t>560956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>821452</t>
+          <t>808744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>392341</t>
+          <t>389352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>436364</t>
+          <t>436148</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>969947</t>
+          <t>967495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1289713</t>
+          <t>1293161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>772581</t>
+          <t>761251</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1102113</t>
+          <t>1094074</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1277459</t>
+          <t>1272239</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1863471</t>
+          <t>1826627</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2191821</t>
+          <t>2207379</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2871650</t>
+          <t>2865676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2357704</t>
+          <t>2365743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2687236</t>
+          <t>2698566</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1795964</t>
+          <t>1832808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2381976</t>
+          <t>2387196</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4247602</t>
+          <t>4253576</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4927431</t>
+          <t>4911873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>51056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>43009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87018</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219646</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242891</t>
+          <t>243063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218152</t>
+          <t>217829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239585</t>
+          <t>239329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445916</t>
+          <t>444014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477133</t>
+          <t>476486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38743</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>67049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76636</t>
+          <t>78226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94227</t>
+          <t>94696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134998</t>
+          <t>134870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426728</t>
+          <t>426026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454332</t>
+          <t>454644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426332</t>
+          <t>424742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454239</t>
+          <t>453402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>861045</t>
+          <t>861173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901816</t>
+          <t>901347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62692</t>
+          <t>60582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49544</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>77918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93328</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130501</t>
+          <t>132509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256154</t>
+          <t>258264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282201</t>
+          <t>282956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257046</t>
+          <t>257494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285868</t>
+          <t>286572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>523757</t>
+          <t>521749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>560930</t>
+          <t>561142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>32275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56365</t>
+          <t>56791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>76125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88571</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124267</t>
+          <t>123637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302306</t>
+          <t>301880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>325502</t>
+          <t>326396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295431</t>
+          <t>295331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322232</t>
+          <t>322715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>605860</t>
+          <t>606490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>641556</t>
+          <t>642718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>42825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53814</t>
+          <t>53562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58114</t>
+          <t>59174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89512</t>
+          <t>89603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160796</t>
+          <t>160483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181322</t>
+          <t>180253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152938</t>
+          <t>153190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175926</t>
+          <t>176171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>320548</t>
+          <t>320457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351946</t>
+          <t>350886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>48171</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>68333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102727</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223438</t>
+          <t>222640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245471</t>
+          <t>245102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215423</t>
+          <t>214188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>241662</t>
+          <t>240334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446228</t>
+          <t>445856</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479961</t>
+          <t>480622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77020</t>
+          <t>76241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112725</t>
+          <t>112092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>91512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130636</t>
+          <t>130385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177884</t>
+          <t>176238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229114</t>
+          <t>228059</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>501452</t>
+          <t>502085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537157</t>
+          <t>537936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>507583</t>
+          <t>507834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545699</t>
+          <t>546707</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1023282</t>
+          <t>1024337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1074512</t>
+          <t>1076158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94366</t>
+          <t>96299</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133940</t>
+          <t>133234</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>95645</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>138294</t>
+          <t>138913</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>204039</t>
+          <t>202924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>260040</t>
+          <t>259339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>609855</t>
+          <t>610561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>649429</t>
+          <t>647496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645217</t>
+          <t>644598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>686832</t>
+          <t>687866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1267266</t>
+          <t>1267967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1323267</t>
+          <t>1324382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>417913</t>
+          <t>416507</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>490096</t>
+          <t>494851</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>490061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>574991</t>
+          <t>578056</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>933527</t>
+          <t>932541</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1045896</t>
+          <t>1048028</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2784683</t>
+          <t>2779928</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2856866</t>
+          <t>2858272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2802309</t>
+          <t>2799244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2883217</t>
+          <t>2887239</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5606183</t>
+          <t>5604051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5718552</t>
+          <t>5719538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63472</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77853</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118129</t>
+          <t>116229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231266</t>
+          <t>230296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257365</t>
+          <t>257812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224689</t>
+          <t>225723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251657</t>
+          <t>252318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463854</t>
+          <t>465754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504130</t>
+          <t>504309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110594</t>
+          <t>109005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74475</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109852</t>
+          <t>110203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153784</t>
+          <t>153561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205315</t>
+          <t>207851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394933</t>
+          <t>396522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432010</t>
+          <t>432217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>413913</t>
+          <t>413562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449290</t>
+          <t>449500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823977</t>
+          <t>821441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>875508</t>
+          <t>875731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>54245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82582</t>
+          <t>84166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50458</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79161</t>
+          <t>79349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111325</t>
+          <t>110195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152660</t>
+          <t>150561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239490</t>
+          <t>237906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>267827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260788</t>
+          <t>260600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289491</t>
+          <t>291107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509361</t>
+          <t>511460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550696</t>
+          <t>551826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51488</t>
+          <t>51994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83142</t>
+          <t>83698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76627</t>
+          <t>78112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>109969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135796</t>
+          <t>136302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184772</t>
+          <t>181440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290840</t>
+          <t>290284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322494</t>
+          <t>321988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>278593</t>
+          <t>278982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>312324</t>
+          <t>310839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578161</t>
+          <t>581493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627137</t>
+          <t>626631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>32353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>55685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>63972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96150</t>
+          <t>95007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>163146</t>
+          <t>163330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>185845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164136</t>
+          <t>163906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188682</t>
+          <t>187238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335044</t>
+          <t>336187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368299</t>
+          <t>367222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45325</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51276</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78694</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103148</t>
+          <t>102025</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141204</t>
+          <t>141401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200013</t>
+          <t>200488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228656</t>
+          <t>227493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201337</t>
+          <t>198811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228755</t>
+          <t>228773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>412808</t>
+          <t>412611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>450864</t>
+          <t>451987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92674</t>
+          <t>95516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135088</t>
+          <t>136298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138082</t>
+          <t>138634</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204398</t>
+          <t>203952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262817</t>
+          <t>262559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>527700</t>
+          <t>526490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>570114</t>
+          <t>567272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>555771</t>
+          <t>555219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>594944</t>
+          <t>598465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1093824</t>
+          <t>1094082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1152243</t>
+          <t>1152689</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>102214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146643</t>
+          <t>144479</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111937</t>
+          <t>112078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155344</t>
+          <t>153894</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>227879</t>
+          <t>229874</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>290242</t>
+          <t>288035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630420</t>
+          <t>632584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>673284</t>
+          <t>674849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>668509</t>
+          <t>669959</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>711916</t>
+          <t>711775</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1310674</t>
+          <t>1312881</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1373037</t>
+          <t>1371042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561934</t>
+          <t>559303</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>651223</t>
+          <t>651651</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>603682</t>
+          <t>601675</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>697331</t>
+          <t>696575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1180465</t>
+          <t>1188590</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1318056</t>
+          <t>1322663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2770532</t>
+          <t>2770104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2859821</t>
+          <t>2862452</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2859907</t>
+          <t>2860663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2953556</t>
+          <t>2955563</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5660937</t>
+          <t>5656330</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5798528</t>
+          <t>5790403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56833</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62467</t>
+          <t>61236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>73405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110423</t>
+          <t>109244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236928</t>
+          <t>237591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>262612</t>
+          <t>261528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226236</t>
+          <t>227467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253727</t>
+          <t>253761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>472041</t>
+          <t>473220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511020</t>
+          <t>509059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64819</t>
+          <t>63511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97940</t>
+          <t>96100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55402</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86550</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124574</t>
+          <t>129112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174424</t>
+          <t>175923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404635</t>
+          <t>406475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437756</t>
+          <t>439064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436534</t>
+          <t>435135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467682</t>
+          <t>468333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>851235</t>
+          <t>849736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901085</t>
+          <t>896547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>47288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>74316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,82 +8080,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>72567</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58740</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>89729</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>21,58%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>26,68%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>132310</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>111075</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>151880</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>23,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72567</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>57702</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>89600</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>132310</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>114399</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>155894</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244696</t>
+          <t>244249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271080</t>
+          <t>271277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,82 +8193,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>263742</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>246580</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>277569</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>78,42%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>73,32%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>522564</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>502994</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>543799</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>76,81%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>263742</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>246709</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>278607</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>522564</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>498980</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>540475</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57422</t>
+          <t>57628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>87694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67365</t>
+          <t>67732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99910</t>
+          <t>102010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129577</t>
+          <t>131176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178476</t>
+          <t>175766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282414</t>
+          <t>282270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312542</t>
+          <t>312336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287373</t>
+          <t>285273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>319918</t>
+          <t>319551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578771</t>
+          <t>581481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627670</t>
+          <t>626071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>42653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43947</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>72569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172557</t>
+          <t>172838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191743</t>
+          <t>192129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175989</t>
+          <t>175934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197673</t>
+          <t>197271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356197</t>
+          <t>357239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>385861</t>
+          <t>385033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>39702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63893</t>
+          <t>64828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78469</t>
+          <t>79060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95226</t>
+          <t>97256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199230</t>
+          <t>198295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224724</t>
+          <t>223421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194646</t>
+          <t>194055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222680</t>
+          <t>221806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400784</t>
+          <t>399947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>441012</t>
+          <t>438982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90298</t>
+          <t>90862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129954</t>
+          <t>131323</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113346</t>
+          <t>111739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157134</t>
+          <t>154716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214920</t>
+          <t>210014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274718</t>
+          <t>268470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526604</t>
+          <t>525235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>566260</t>
+          <t>565696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>534160</t>
+          <t>536578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>577948</t>
+          <t>579555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1073134</t>
+          <t>1079382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1132932</t>
+          <t>1137838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>75195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>111710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95324</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>138346</t>
+          <t>139906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182422</t>
+          <t>179791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237269</t>
+          <t>234560</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>665699</t>
+          <t>666873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>701587</t>
+          <t>703388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>687821</t>
+          <t>686261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>730843</t>
+          <t>731787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1367481</t>
+          <t>1370190</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1422328</t>
+          <t>1424959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>496907</t>
+          <t>492829</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>576882</t>
+          <t>574832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>568059</t>
+          <t>564882</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>667564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1085633</t>
+          <t>1088262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1210414</t>
+          <t>1210238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2817468</t>
+          <t>2819518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2897443</t>
+          <t>2901521</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2880519</t>
+          <t>2876978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2976483</t>
+          <t>2979660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5728478</t>
+          <t>5728654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5853259</t>
+          <t>5850630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88939</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71781</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106535</t>
+          <t>107809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>104967</t>
+          <t>105535</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92515</t>
+          <t>92958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118940</t>
+          <t>118193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>193905</t>
+          <t>195842</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174264</t>
+          <t>176439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216546</t>
+          <t>217032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>222504</t>
+          <t>228537</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204908</t>
+          <t>211036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239662</t>
+          <t>243173</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>184668</t>
+          <t>210526</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170695</t>
+          <t>197868</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197120</t>
+          <t>223103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>407172</t>
+          <t>439064</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384531</t>
+          <t>417874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426813</t>
+          <t>458467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>139642</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116303</t>
+          <t>122729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>163911</t>
+          <t>167862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>167372</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142478</t>
+          <t>147476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179434</t>
+          <t>187024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>300791</t>
+          <t>312764</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271377</t>
+          <t>285460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>333163</t>
+          <t>345172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>378748</t>
+          <t>385255</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354479</t>
+          <t>362785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402087</t>
+          <t>407918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>353820</t>
+          <t>379122</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335535</t>
+          <t>359470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372491</t>
+          <t>399018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>732568</t>
+          <t>764377</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700196</t>
+          <t>731969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>761982</t>
+          <t>791681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86636</t>
+          <t>85263</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71874</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100563</t>
+          <t>99091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108912</t>
+          <t>111383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94123</t>
+          <t>96684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122824</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>195548</t>
+          <t>196645</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175578</t>
+          <t>175150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217095</t>
+          <t>214776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>229414</t>
+          <t>230730</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215487</t>
+          <t>216902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244176</t>
+          <t>242423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>240216</t>
+          <t>244998</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226304</t>
+          <t>230358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255005</t>
+          <t>259697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>469630</t>
+          <t>475730</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>448083</t>
+          <t>457599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>489600</t>
+          <t>497225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>100909</t>
+          <t>109110</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>88561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119202</t>
+          <t>129144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137284</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80836</t>
+          <t>131389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173707</t>
+          <t>166067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>238193</t>
+          <t>257000</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171174</t>
+          <t>231544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278664</t>
+          <t>280954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>211648</t>
+          <t>264035</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193355</t>
+          <t>244001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229722</t>
+          <t>284584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>338434</t>
+          <t>274071</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302011</t>
+          <t>255894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394882</t>
+          <t>290572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>550081</t>
+          <t>538107</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>509610</t>
+          <t>514153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617100</t>
+          <t>563563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>70,88%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>55996</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66591</t>
+          <t>71535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>85664</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>75029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90516</t>
+          <t>95953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>137038</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124247</t>
+          <t>130505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150431</t>
+          <t>159515</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>122746</t>
+          <t>145925</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112151</t>
+          <t>134130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132427</t>
+          <t>156420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>127232</t>
+          <t>141159</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>130870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136830</t>
+          <t>151794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>249978</t>
+          <t>287084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236585</t>
+          <t>272973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262769</t>
+          <t>301983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59758</t>
+          <t>60222</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83287</t>
+          <t>83819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95084</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84117</t>
+          <t>84745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>108846</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>166247</t>
+          <t>169022</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148471</t>
+          <t>151652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183570</t>
+          <t>187113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>198473</t>
+          <t>199466</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>186349</t>
+          <t>186888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209878</t>
+          <t>210485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>161972</t>
+          <t>165969</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150723</t>
+          <t>154904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172939</t>
+          <t>179005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>360445</t>
+          <t>365435</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343122</t>
+          <t>347344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>378221</t>
+          <t>382805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>197308</t>
+          <t>235613</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172680</t>
+          <t>208707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221961</t>
+          <t>265920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>438752</t>
+          <t>281112</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>297467</t>
+          <t>255282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>646574</t>
+          <t>306406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>636060</t>
+          <t>516725</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484226</t>
+          <t>477510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>925864</t>
+          <t>554208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>426971</t>
+          <t>484074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>402318</t>
+          <t>453767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>451599</t>
+          <t>510980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>410513</t>
+          <t>490945</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>465651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>551798</t>
+          <t>516775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>837484</t>
+          <t>975019</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547680</t>
+          <t>937536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>989318</t>
+          <t>1014234</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>262849</t>
+          <t>295768</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119976</t>
+          <t>269009</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367764</t>
+          <t>323603</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>301387</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279244</t>
+          <t>320021</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>326040</t>
+          <t>372380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>564236</t>
+          <t>643085</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350951</t>
+          <t>605547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>676617</t>
+          <t>679751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>665871</t>
+          <t>502304</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>560956</t>
+          <t>474469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>808744</t>
+          <t>529063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>414005</t>
+          <t>483292</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>389352</t>
+          <t>458229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>436148</t>
+          <t>510588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1079876</t>
+          <t>985596</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>967495</t>
+          <t>948930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1293161</t>
+          <t>1023134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>761251</t>
+          <t>1038257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1094074</t>
+          <t>1148687</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1272239</t>
+          <t>1296631</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1826627</t>
+          <t>1403302</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2207379</t>
+          <t>2365011</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2865676</t>
+          <t>2513361</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2456374</t>
+          <t>2440327</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2365743</t>
+          <t>2384075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2698566</t>
+          <t>2494505</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2230859</t>
+          <t>2390084</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1832808</t>
+          <t>2330835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2387196</t>
+          <t>2437506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4687233</t>
+          <t>4830411</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4253576</t>
+          <t>4753538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4911873</t>
+          <t>4901888</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
